--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -585,6 +585,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -599,6 +603,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -668,7 +676,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -690,7 +700,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -712,7 +724,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -734,7 +748,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -756,7 +772,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -778,7 +796,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -800,7 +820,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -822,7 +844,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -844,7 +868,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -866,7 +892,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -888,7 +916,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -910,7 +940,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -932,7 +964,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>9</v>
       </c>
@@ -954,7 +988,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -976,7 +1012,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -998,7 +1036,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -1020,7 +1060,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>8</v>
       </c>
@@ -1042,7 +1084,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>8</v>
       </c>
@@ -1064,7 +1108,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>
@@ -1086,7 +1132,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1108,7 +1156,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>7</v>
       </c>
@@ -1130,7 +1180,9 @@
       <c r="C37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -1152,7 +1204,9 @@
       <c r="C38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -1298,6 +1352,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1313,6 +1371,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1382,7 +1444,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -1404,7 +1468,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1426,7 +1492,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -1448,7 +1516,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1470,7 +1540,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -1492,7 +1564,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -1514,7 +1588,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -1536,7 +1612,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -1558,7 +1636,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -1580,7 +1660,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1602,7 +1684,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -1624,7 +1708,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -1646,7 +1732,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -1668,7 +1756,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -1690,7 +1780,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -1712,7 +1804,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -1734,7 +1828,9 @@
       <c r="C32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -1756,7 +1852,9 @@
       <c r="C33" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>8</v>
       </c>
@@ -1778,7 +1876,9 @@
       <c r="C34" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -1924,6 +2024,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1937,6 +2041,10 @@
 Workshop		: 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2006,7 +2114,9 @@
       <c r="C16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -2028,7 +2138,9 @@
       <c r="C17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -2050,7 +2162,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -2072,7 +2186,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -2094,7 +2210,9 @@
       <c r="C20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -2116,7 +2234,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -2138,7 +2258,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -2160,7 +2282,9 @@
       <c r="C23" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -2182,7 +2306,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -2204,7 +2330,9 @@
       <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -2226,7 +2354,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -2248,7 +2378,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -2270,7 +2402,9 @@
       <c r="C28" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -2292,7 +2426,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -2314,7 +2450,9 @@
       <c r="C30" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -2336,7 +2474,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -2358,7 +2498,9 @@
       <c r="C32" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -2380,7 +2522,9 @@
       <c r="C33" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -2402,7 +2546,9 @@
       <c r="C34" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -2424,7 +2570,9 @@
       <c r="C35" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>5</v>
       </c>
@@ -2446,7 +2594,9 @@
       <c r="C36" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -2468,7 +2618,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>8</v>
       </c>
@@ -2490,7 +2642,9 @@
       <c r="C38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -2512,7 +2666,9 @@
       <c r="C39" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>8</v>
       </c>
@@ -2534,7 +2690,9 @@
       <c r="C40" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>6</v>
       </c>
@@ -2556,7 +2714,9 @@
       <c r="C41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>4</v>
       </c>
@@ -2578,7 +2738,9 @@
       <c r="C42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>6</v>
       </c>
@@ -2600,7 +2762,9 @@
       <c r="C43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>6</v>
       </c>
@@ -2622,7 +2786,9 @@
       <c r="C44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>4</v>
       </c>
@@ -2768,6 +2934,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2781,6 +2951,10 @@
 Workshop/ lab – 800 sft (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2850,7 +3024,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2872,7 +3048,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2894,7 +3072,9 @@
       <c r="C18" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -2916,7 +3096,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -2938,7 +3120,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -2960,7 +3144,9 @@
       <c r="C21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>5</v>
       </c>
@@ -2982,7 +3168,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -3004,7 +3192,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -3026,7 +3216,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -3048,7 +3240,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -3070,7 +3264,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -3092,7 +3288,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -3114,7 +3312,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -3136,7 +3336,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -3158,7 +3360,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -3180,7 +3384,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -3202,7 +3408,9 @@
       <c r="C32" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -3224,7 +3432,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -3246,7 +3456,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -3392,6 +3604,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3406,6 +3622,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3475,7 +3695,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3497,7 +3719,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3519,7 +3743,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -3541,7 +3767,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -3563,7 +3791,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -3585,7 +3815,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -3607,7 +3839,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -3629,7 +3863,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -3651,7 +3887,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -3673,7 +3911,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -3695,7 +3935,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -3717,7 +3959,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -3739,7 +3983,9 @@
       <c r="C28" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -3761,7 +4007,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -3783,7 +4031,9 @@
       <c r="C30" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -3805,7 +4055,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -3827,7 +4079,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -3849,7 +4103,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -3871,7 +4127,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>8</v>
       </c>
@@ -3893,7 +4151,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>6</v>
       </c>
@@ -3915,7 +4175,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>5</v>
       </c>
@@ -3937,7 +4199,9 @@
       <c r="C37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>7</v>
       </c>
@@ -3959,7 +4223,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -4105,6 +4371,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4119,6 +4389,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4188,7 +4462,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -4210,7 +4486,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -4232,7 +4510,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -4254,7 +4534,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -4276,7 +4558,9 @@
       <c r="C20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -4298,7 +4582,9 @@
       <c r="C21" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -4320,7 +4606,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -4342,7 +4630,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -4364,7 +4654,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -4386,7 +4678,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>9</v>
       </c>
@@ -4408,7 +4702,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -4430,7 +4726,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -4452,7 +4750,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -4474,7 +4774,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -4496,7 +4798,9 @@
       <c r="C30" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -4518,7 +4822,9 @@
       <c r="C31" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -4540,7 +4846,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -4562,7 +4870,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -4584,7 +4894,9 @@
       <c r="C34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -4730,6 +5042,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -4743,6 +5059,10 @@
 Workshop/Lab	: 800-1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4812,7 +5132,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -4834,7 +5156,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>7</v>
       </c>
@@ -4856,7 +5180,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>7</v>
       </c>
@@ -4878,7 +5204,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -4900,7 +5228,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -4922,7 +5252,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -4944,7 +5276,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -4966,7 +5300,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -4988,7 +5324,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -5010,7 +5348,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -5032,7 +5372,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -5054,7 +5396,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -5076,7 +5420,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -5098,7 +5444,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -5120,7 +5468,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -5142,7 +5492,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -5164,7 +5516,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>8</v>
       </c>
@@ -5186,7 +5540,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -5332,6 +5688,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -5347,6 +5707,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5416,7 +5780,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -5438,7 +5804,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -5460,7 +5828,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -5482,7 +5852,9 @@
       <c r="C19" s="9" t="n">
         <v>112</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -5504,7 +5876,9 @@
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -5526,7 +5900,9 @@
       <c r="C21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -5548,7 +5924,9 @@
       <c r="C22" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -5570,7 +5948,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -5592,7 +5972,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -5614,7 +5996,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -5636,7 +6020,9 @@
       <c r="C26" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -5658,7 +6044,9 @@
       <c r="C27" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -5680,7 +6068,9 @@
       <c r="C28" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -5826,6 +6216,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -5840,6 +6234,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -5909,7 +6307,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -5931,7 +6331,9 @@
       <c r="C17" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -5953,7 +6355,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -5975,7 +6379,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -5997,7 +6403,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -6019,7 +6427,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -6041,7 +6451,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -6063,7 +6475,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -6089,7 +6503,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -6115,7 +6531,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -6141,7 +6559,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -6291,6 +6711,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -6305,6 +6729,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -6374,7 +6802,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -6400,7 +6830,9 @@
       <c r="C17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>8</v>
       </c>
@@ -6426,7 +6858,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -6452,7 +6886,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -6478,7 +6914,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -6504,7 +6942,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -6530,7 +6970,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -6556,7 +6998,9 @@
       <c r="C23" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -6582,7 +7026,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -6608,7 +7054,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -6634,7 +7082,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>10</v>
       </c>
@@ -6660,7 +7110,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -6686,7 +7138,9 @@
       <c r="C28" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -6712,7 +7166,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>9</v>
       </c>
@@ -6738,7 +7194,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -6764,7 +7222,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -6790,7 +7250,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -6816,7 +7278,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -6842,7 +7306,9 @@
       <c r="C34" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -6868,7 +7334,9 @@
       <c r="C35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -6894,7 +7362,9 @@
       <c r="C36" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -6920,7 +7390,9 @@
       <c r="C37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -7070,6 +7542,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -7083,6 +7559,10 @@
 Workshop/ lab – 1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -7152,7 +7632,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -7174,7 +7656,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -7196,7 +7680,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -7218,7 +7704,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -7240,7 +7728,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -7262,7 +7752,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -7284,7 +7776,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -7306,7 +7800,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -7328,7 +7824,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>9</v>
       </c>
@@ -7350,7 +7848,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -7372,7 +7872,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -7394,7 +7896,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -7416,7 +7920,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -7438,7 +7944,9 @@
       <c r="C29" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -7460,7 +7968,9 @@
       <c r="C30" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -7482,7 +7992,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -7504,7 +8016,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -7526,7 +8040,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -7548,7 +8064,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>5</v>
       </c>
@@ -7570,7 +8088,9 @@
       <c r="C35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>5</v>
       </c>
@@ -7592,7 +8112,9 @@
       <c r="C36" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -7614,7 +8136,9 @@
       <c r="C37" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -7636,7 +8160,9 @@
       <c r="C38" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -7658,7 +8184,9 @@
       <c r="C39" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
@@ -7680,7 +8208,9 @@
       <c r="C40" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>6</v>
       </c>
@@ -7702,7 +8232,9 @@
       <c r="C41" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>6</v>
       </c>
@@ -7724,7 +8256,9 @@
       <c r="C42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
@@ -7746,7 +8280,9 @@
       <c r="C43" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>6</v>
       </c>
@@ -7768,7 +8304,9 @@
       <c r="C44" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>4</v>
       </c>
@@ -7790,7 +8328,9 @@
       <c r="C45" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>5</v>
       </c>
@@ -7812,7 +8352,9 @@
       <c r="C46" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>3</v>
       </c>
@@ -7834,7 +8376,9 @@
       <c r="C47" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="9" t="n">
         <v>3</v>
       </c>
@@ -7856,7 +8400,9 @@
       <c r="C48" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="9" t="n"/>
+      <c r="D48" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="9" t="n">
         <v>3</v>
       </c>
@@ -7878,7 +8424,9 @@
       <c r="C49" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D49" s="9" t="n"/>
+      <c r="D49" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="9" t="n">
         <v>4</v>
       </c>
@@ -7900,7 +8448,9 @@
       <c r="C50" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D50" s="9" t="n"/>
+      <c r="D50" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" s="9" t="n">
         <v>3</v>
       </c>
@@ -7922,7 +8472,9 @@
       <c r="C51" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D51" s="9" t="n"/>
+      <c r="D51" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" s="9" t="n">
         <v>3</v>
       </c>
@@ -7991,9 +8543,9 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A55:E55"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A52:D52"/>
     <mergeCell ref="A54:G54"/>
@@ -8068,6 +8620,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -8080,6 +8636,10 @@
           <t>Classroom cum workshop – 500 - 600 sft (50-55 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -8150,7 +8710,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -8172,7 +8734,9 @@
       <c r="C17" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -8194,7 +8758,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>6</v>
       </c>
@@ -8216,7 +8782,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -8238,7 +8806,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -8260,7 +8830,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -8282,7 +8854,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -8304,7 +8878,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -8326,7 +8902,9 @@
       <c r="C24" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>3</v>
       </c>
@@ -8472,6 +9050,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -8486,6 +9068,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -8555,7 +9141,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -8577,7 +9165,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -8599,7 +9189,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -8621,7 +9213,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -8643,7 +9237,9 @@
       <c r="C20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>4</v>
       </c>
@@ -8665,7 +9261,9 @@
       <c r="C21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -8687,7 +9285,9 @@
       <c r="C22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>3</v>
       </c>
@@ -8709,7 +9309,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -8731,7 +9333,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -8753,7 +9357,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -8775,7 +9381,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -8797,7 +9405,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -8819,7 +9429,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -8841,7 +9453,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -8863,7 +9477,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -8885,7 +9501,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -9031,6 +9649,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -9045,6 +9667,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -9114,7 +9740,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -9136,7 +9764,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -9158,7 +9788,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -9180,7 +9812,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -9202,7 +9836,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -9224,7 +9860,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -9246,7 +9884,9 @@
       <c r="C22" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -9268,7 +9908,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -9290,7 +9932,9 @@
       <c r="C24" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -9312,7 +9956,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -9334,7 +9980,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -9356,7 +10004,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -9378,7 +10028,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -9400,7 +10052,9 @@
       <c r="C29" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -9422,7 +10076,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -9491,9 +10147,9 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="A33:G33"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A32:E32"/>
@@ -9568,6 +10224,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -9583,6 +10243,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -9652,7 +10316,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -9674,7 +10340,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -9696,7 +10364,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -9718,7 +10388,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -9740,7 +10412,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -9762,7 +10436,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -9784,7 +10460,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -9806,7 +10484,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>4</v>
       </c>
@@ -9828,7 +10508,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>3</v>
       </c>
@@ -9850,7 +10532,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -9872,7 +10556,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -9894,7 +10580,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -9916,7 +10604,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -9938,7 +10628,9 @@
       <c r="C29" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -9960,7 +10652,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -9982,7 +10676,9 @@
       <c r="C31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -10004,7 +10700,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -10150,6 +10848,10 @@
           <t>SICIP required space for 30 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -10165,6 +10867,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -10234,7 +10940,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -10256,7 +10964,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -10278,7 +10988,9 @@
       <c r="C18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -10300,7 +11012,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -10322,7 +11036,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -10344,7 +11060,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -10366,7 +11084,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -10388,7 +11108,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -10410,7 +11132,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -10432,7 +11156,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -10454,7 +11180,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -10476,7 +11204,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -10498,7 +11228,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -10520,7 +11252,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -10666,6 +11400,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -10681,6 +11419,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -10750,7 +11492,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -10772,7 +11516,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -10794,7 +11540,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -10816,7 +11564,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -10838,7 +11588,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>10</v>
       </c>
@@ -10860,7 +11612,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -10882,7 +11636,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -10904,7 +11660,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -10926,7 +11684,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -10948,7 +11708,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -10970,7 +11732,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -10992,7 +11756,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -11014,7 +11780,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -11036,7 +11804,9 @@
       <c r="C29" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -11058,7 +11828,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -11080,7 +11852,9 @@
       <c r="C31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -11102,7 +11876,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -11124,7 +11900,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -11146,7 +11924,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -11292,6 +12072,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -11306,6 +12090,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -11375,7 +12163,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -11397,7 +12187,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -11419,7 +12211,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -11441,7 +12235,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -11463,7 +12259,9 @@
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -11485,7 +12283,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -11507,7 +12307,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -11529,7 +12331,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -11551,7 +12355,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -11573,7 +12379,9 @@
       <c r="C25" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -11595,7 +12403,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -11617,7 +12427,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -11639,7 +12451,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -11661,7 +12475,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -11683,7 +12499,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -11705,7 +12523,9 @@
       <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -11851,6 +12671,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -11865,6 +12689,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -11934,7 +12762,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -11956,7 +12786,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -11978,7 +12810,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -12000,7 +12834,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -12022,7 +12858,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -12044,7 +12882,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -12066,7 +12906,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>5</v>
       </c>
@@ -12088,7 +12930,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -12110,7 +12954,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -12132,7 +12978,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -12154,7 +13002,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -12176,7 +13026,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -12198,7 +13050,9 @@
       <c r="C28" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -12220,7 +13074,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -12242,7 +13098,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -12264,7 +13122,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -12286,7 +13146,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -12308,7 +13170,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -12455,6 +13319,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -12469,6 +13337,10 @@
 Workshop		: 700-800 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -12539,7 +13411,9 @@
       <c r="C16" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -12561,7 +13435,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>10</v>
       </c>
@@ -12583,7 +13459,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -12605,7 +13483,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -12627,7 +13507,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -12649,7 +13531,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -12671,7 +13555,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -12693,7 +13579,9 @@
       <c r="C23" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>4</v>
       </c>
@@ -12715,7 +13603,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -12737,7 +13627,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -12759,7 +13651,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -12785,7 +13679,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -12807,7 +13703,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -12953,6 +13851,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -12967,6 +13869,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -13036,7 +13942,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -13058,7 +13966,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -13080,7 +13990,9 @@
       <c r="C18" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -13102,7 +14014,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -13124,7 +14038,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -13146,7 +14062,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -13168,7 +14086,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -13190,7 +14110,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -13212,7 +14134,9 @@
       <c r="C24" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -13234,7 +14158,9 @@
       <c r="C25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -13256,7 +14182,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -13278,7 +14206,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -13300,7 +14230,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -13322,7 +14254,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -13344,7 +14278,9 @@
       <c r="C30" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -13366,7 +14302,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -13388,7 +14326,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -13410,7 +14350,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -13432,7 +14374,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>7</v>
       </c>
@@ -13454,7 +14398,9 @@
       <c r="C35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -13476,7 +14422,9 @@
       <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -13498,7 +14446,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -13520,7 +14470,9 @@
       <c r="C38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -13666,6 +14618,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -13679,6 +14635,10 @@
 Workshop/ lab – 1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -13748,7 +14708,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -13770,7 +14732,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -13792,7 +14756,9 @@
       <c r="C18" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -13814,7 +14780,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -13836,7 +14804,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -13858,7 +14828,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -13880,7 +14852,9 @@
       <c r="C22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -13902,7 +14876,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -13924,7 +14900,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -13946,7 +14924,9 @@
       <c r="C25" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -13968,7 +14948,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -13990,7 +14972,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -14012,7 +14996,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -14034,7 +15020,9 @@
       <c r="C29" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -14056,7 +15044,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -14078,7 +15068,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -14100,7 +15092,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -14122,7 +15116,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -14144,7 +15140,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -14166,7 +15164,9 @@
       <c r="C35" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>6</v>
       </c>
@@ -14188,7 +15188,9 @@
       <c r="C36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>6</v>
       </c>
@@ -14210,7 +15212,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
@@ -14232,7 +15236,9 @@
       <c r="C38" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -14254,7 +15260,9 @@
       <c r="C39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
@@ -14276,7 +15284,9 @@
       <c r="C40" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>6</v>
       </c>
@@ -14298,7 +15308,9 @@
       <c r="C41" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>4</v>
       </c>
@@ -14320,7 +15332,9 @@
       <c r="C42" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>5</v>
       </c>
@@ -14342,7 +15356,9 @@
       <c r="C43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>5</v>
       </c>
@@ -14364,7 +15380,9 @@
       <c r="C44" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>7</v>
       </c>
@@ -14386,7 +15404,9 @@
       <c r="C45" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>7</v>
       </c>
@@ -14408,7 +15428,9 @@
       <c r="C46" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>4</v>
       </c>
@@ -14430,7 +15452,9 @@
       <c r="C47" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="9" t="n"/>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="9" t="n">
         <v>3</v>
       </c>
@@ -14452,7 +15476,9 @@
       <c r="C48" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D48" s="9" t="n"/>
+      <c r="D48" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="9" t="n">
         <v>4</v>
       </c>
@@ -14598,6 +15624,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -14611,6 +15641,10 @@
 Workshop/ lab – 800 sft. (75 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -14680,7 +15714,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -14702,7 +15738,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -14724,7 +15762,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -14758,7 +15798,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -14784,7 +15826,9 @@
       <c r="C20" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
@@ -14806,7 +15850,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -14828,7 +15874,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -14854,7 +15902,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -14876,7 +15926,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -14898,7 +15950,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -14920,7 +15974,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -14942,7 +15998,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -14964,7 +16022,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -14986,7 +16046,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -15008,7 +16070,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -15034,7 +16098,9 @@
       <c r="C31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>7</v>
       </c>
@@ -15060,7 +16126,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -15082,7 +16150,9 @@
       <c r="C33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -15104,7 +16174,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -15126,7 +16198,9 @@
       <c r="C35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -15148,7 +16222,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -15170,7 +16246,9 @@
       <c r="C37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>7</v>
       </c>
@@ -15192,7 +16270,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>4</v>
       </c>
@@ -15214,7 +16294,9 @@
       <c r="C39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -15236,7 +16318,9 @@
       <c r="C40" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>4</v>
       </c>
@@ -15258,7 +16342,9 @@
       <c r="C41" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -15280,7 +16366,9 @@
       <c r="C42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
@@ -15426,6 +16514,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -15440,6 +16532,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -15509,7 +16605,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -15531,7 +16629,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -15553,7 +16653,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>7</v>
       </c>
@@ -15575,7 +16677,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -15597,7 +16701,9 @@
       <c r="C20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -15619,7 +16725,9 @@
       <c r="C21" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -15641,7 +16749,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -15667,7 +16777,9 @@
       <c r="C23" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -15693,7 +16805,9 @@
       <c r="C24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -15719,7 +16833,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -15741,7 +16857,9 @@
       <c r="C26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>3</v>
       </c>
@@ -15763,7 +16881,9 @@
       <c r="C27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>3</v>
       </c>
@@ -15785,7 +16905,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>3</v>
       </c>
@@ -15807,7 +16929,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -15829,7 +16953,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>3</v>
       </c>
@@ -15851,7 +16977,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -15873,7 +17001,9 @@
       <c r="C32" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -15895,7 +17025,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -15917,7 +17049,9 @@
       <c r="C34" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>3</v>
       </c>
@@ -15939,7 +17073,9 @@
       <c r="C35" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>3</v>
       </c>
@@ -15961,7 +17097,9 @@
       <c r="C36" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -15983,7 +17121,9 @@
       <c r="C37" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>3</v>
       </c>
@@ -16005,7 +17145,9 @@
       <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -16027,7 +17169,9 @@
       <c r="C39" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
@@ -16049,7 +17193,9 @@
       <c r="C40" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>3</v>
       </c>
@@ -16071,7 +17217,9 @@
       <c r="C41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -16097,7 +17245,9 @@
       <c r="C42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E42" s="9" t="n">
         <v>3</v>
       </c>
@@ -16119,7 +17269,9 @@
       <c r="C43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" s="9" t="n">
         <v>3</v>
       </c>
@@ -16141,7 +17293,9 @@
       <c r="C44" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" s="9" t="n">
         <v>3</v>
       </c>
@@ -16163,7 +17317,9 @@
       <c r="C45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E45" s="9" t="n">
         <v>3</v>
       </c>
@@ -16185,7 +17341,9 @@
       <c r="C46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="9" t="n">
         <v>3</v>
       </c>
@@ -16331,6 +17489,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -16345,6 +17507,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -16414,7 +17580,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>9</v>
       </c>
@@ -16436,7 +17604,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>8</v>
       </c>
@@ -16458,7 +17628,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -16480,7 +17652,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -16502,7 +17676,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -16524,7 +17700,9 @@
       <c r="C21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -16546,7 +17724,9 @@
       <c r="C22" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -16568,7 +17748,9 @@
       <c r="C23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>4</v>
       </c>
@@ -16590,7 +17772,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -16612,7 +17796,9 @@
       <c r="C25" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -16634,7 +17820,9 @@
       <c r="C26" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -16656,7 +17844,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -16678,7 +17868,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -16824,6 +18016,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -16836,6 +18032,10 @@
           <t>Class room cum Workshop lab: 700-800 sft.</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -16905,7 +18105,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -16927,7 +18129,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
@@ -16949,7 +18153,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -16971,7 +18177,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -16993,7 +18201,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -17015,7 +18225,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -17037,7 +18249,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -17059,7 +18273,9 @@
       <c r="C23" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -17081,7 +18297,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -17103,7 +18321,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
@@ -17125,7 +18345,9 @@
       <c r="C26" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>7</v>
       </c>
@@ -17147,7 +18369,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -17169,7 +18393,9 @@
       <c r="C28" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -17191,7 +18417,9 @@
       <c r="C29" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -17213,7 +18441,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -17235,7 +18465,9 @@
       <c r="C31" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -17257,7 +18489,9 @@
       <c r="C32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -17279,7 +18513,9 @@
       <c r="C33" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -17301,7 +18537,9 @@
       <c r="C34" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -17323,7 +18561,9 @@
       <c r="C35" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -17345,7 +18585,9 @@
       <c r="C36" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>3</v>
       </c>
@@ -17367,7 +18609,9 @@
       <c r="C37" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>5</v>
       </c>
@@ -17389,7 +18633,9 @@
       <c r="C38" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -17411,7 +18657,9 @@
       <c r="C39" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>7</v>
       </c>
@@ -17433,7 +18681,9 @@
       <c r="C40" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>6</v>
       </c>
@@ -17579,6 +18829,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -17594,6 +18848,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -17663,7 +18921,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -17685,7 +18945,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>6</v>
       </c>
@@ -17707,7 +18969,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -17730,7 +18994,9 @@
       <c r="C19" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>10</v>
       </c>
@@ -17753,7 +19019,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -17775,7 +19043,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -17801,7 +19071,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -17827,7 +19099,9 @@
       <c r="C23" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -17853,7 +19127,9 @@
       <c r="C24" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -17875,7 +19151,9 @@
       <c r="C25" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>3</v>
       </c>
@@ -17897,7 +19175,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -18043,6 +19323,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -18056,6 +19340,10 @@
 Workshop/ Lab	: 800-1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -18125,7 +19413,9 @@
       <c r="C16" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -18147,7 +19437,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>8</v>
       </c>
@@ -18169,7 +19461,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -18191,7 +19485,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>7</v>
       </c>
@@ -18213,7 +19509,9 @@
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -18235,7 +19533,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -18257,7 +19557,9 @@
       <c r="C22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -18279,7 +19581,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -18301,7 +19605,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -18447,6 +19753,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -18460,6 +19770,10 @@
 Workshop		: 800-1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -18529,7 +19843,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -18551,7 +19867,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -18573,7 +19891,9 @@
       <c r="C18" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>10</v>
       </c>
@@ -18595,7 +19915,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -18617,7 +19939,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -18639,7 +19963,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -18661,7 +19987,9 @@
       <c r="C22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -18683,7 +20011,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -18705,7 +20035,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -18727,7 +20059,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>4</v>
       </c>
@@ -18749,7 +20083,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -18771,7 +20107,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -18917,6 +20255,10 @@
           <t>SICIP required space for 25 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -18932,6 +20274,10 @@
 Classroom cum workshop – 1500 sft (140 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -19001,7 +20347,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -19023,7 +20371,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -19045,7 +20395,9 @@
       <c r="C18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -19067,7 +20419,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>4</v>
       </c>
@@ -19089,7 +20443,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -19111,7 +20467,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -19133,7 +20491,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -19155,7 +20515,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -19177,7 +20539,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>8</v>
       </c>
@@ -19199,7 +20563,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -19221,7 +20587,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>

--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -8786,7 +8786,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -8906,7 +8906,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -12862,7 +12862,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -12886,7 +12886,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -12910,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -12934,7 +12934,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -12958,7 +12958,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -12982,7 +12982,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -13006,7 +13006,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -13054,7 +13054,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -13102,7 +13102,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
@@ -13126,7 +13126,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" s="9">
         <f>IFERROR(MIN(C31,D31)*E31/C31,0)</f>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>

--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -13487,7 +13487,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -13511,7 +13511,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -13535,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -13559,7 +13559,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -13583,7 +13583,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -13607,7 +13607,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>

--- a/lab-standards/BMET-lab-standard.xlsx
+++ b/lab-standards/BMET-lab-standard.xlsx
@@ -12239,7 +12239,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" s="9">
         <f>IFERROR(MIN(C19,D19)*E19/C19,0)</f>
@@ -12335,7 +12335,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -12359,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -12407,7 +12407,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -12431,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -12455,7 +12455,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(MIN(C28,D28)*E28/C28,0)</f>
@@ -12503,7 +12503,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(MIN(C30,D30)*E30/C30,0)</f>
